--- a/Documents/CPLD-Digital Clock Material.xlsx
+++ b/Documents/CPLD-Digital Clock Material.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boyud\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C9CD8F-B57F-470F-937A-947973BF6EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1887596-85A4-4DD6-ACFC-431F598BF874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26295" yWindow="1920" windowWidth="22305" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2370" yWindow="2210" windowWidth="17680" windowHeight="8250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="117">
   <si>
     <t>Reference</t>
   </si>
@@ -265,6 +265,117 @@
   </si>
   <si>
     <t>TO-92L leads in-line (large body variant of TO-92), also known as TO-226, wide, drill 0.75mm</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>Capacitor SMD 0201 (0603 Metric), square (rectangular) end terminal, IPC-7351 nominal</t>
+  </si>
+  <si>
+    <t>EPM3064:PLCC127P1765X1765X457-44N</t>
+  </si>
+  <si>
+    <t>Connector_IDC:IDC-Header_2x03_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>Connector_PinHeader_1.00mm:PinHeader_1x15_P1.00mm_Vertical</t>
+  </si>
+  <si>
+    <t>Resistor_SMD:R_0201_0603Metric</t>
+  </si>
+  <si>
+    <t>LED_SMD:LED_PLCC_2835</t>
+  </si>
+  <si>
+    <t>Type-c Charging Protect Modle</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>Button_Switch_THT:SW_PUSH_6mm</t>
+  </si>
+  <si>
+    <t>Connector_USB:USB_C_Receptacle_GCT_USB4125-xx-x-0190_6P_TopMnt_Horizontal</t>
+  </si>
+  <si>
+    <t>New Library:4_Digits_7Seg</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>TP4056</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>DW01A</t>
+  </si>
+  <si>
+    <t>Q5</t>
+  </si>
+  <si>
+    <t>FS8205A</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Package_SO:SOIC-8-1EP_3.9x4.9mm_P1.27mm_EP2.41x3.3mm_ThermalVias</t>
+  </si>
+  <si>
+    <t>Package_TO_SOT_SMD:SOT-23-6</t>
+  </si>
+  <si>
+    <t>SOP65P640X120-8N</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>R23</t>
+  </si>
+  <si>
+    <t>R26</t>
+  </si>
+  <si>
+    <t>1.2k</t>
   </si>
 </sst>
 </file>
@@ -306,13 +417,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -594,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
@@ -635,6 +752,9 @@
       <c r="C3" t="s">
         <v>20</v>
       </c>
+      <c r="D3" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -646,6 +766,9 @@
       <c r="C4" t="s">
         <v>33</v>
       </c>
+      <c r="D4" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -671,6 +794,9 @@
       <c r="C6" t="s">
         <v>30</v>
       </c>
+      <c r="D6" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -682,6 +808,9 @@
       <c r="C7" t="s">
         <v>35</v>
       </c>
+      <c r="D7" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -693,6 +822,9 @@
       <c r="C8" t="s">
         <v>35</v>
       </c>
+      <c r="D8" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -704,6 +836,9 @@
       <c r="C9" t="s">
         <v>23</v>
       </c>
+      <c r="D9" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -715,6 +850,9 @@
       <c r="C10" t="s">
         <v>23</v>
       </c>
+      <c r="D10" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -726,6 +864,9 @@
       <c r="C11" t="s">
         <v>23</v>
       </c>
+      <c r="D11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -737,6 +878,9 @@
       <c r="C12" t="s">
         <v>23</v>
       </c>
+      <c r="D12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -748,6 +892,9 @@
       <c r="C13" t="s">
         <v>23</v>
       </c>
+      <c r="D13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
@@ -759,6 +906,9 @@
       <c r="C14" t="s">
         <v>19</v>
       </c>
+      <c r="D14" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -770,6 +920,9 @@
       <c r="C15" t="s">
         <v>19</v>
       </c>
+      <c r="D15" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -781,6 +934,9 @@
       <c r="C16" t="s">
         <v>19</v>
       </c>
+      <c r="D16" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
@@ -792,6 +948,9 @@
       <c r="C17" t="s">
         <v>19</v>
       </c>
+      <c r="D17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
@@ -803,6 +962,9 @@
       <c r="C18" t="s">
         <v>19</v>
       </c>
+      <c r="D18" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
@@ -814,6 +976,9 @@
       <c r="C19" t="s">
         <v>19</v>
       </c>
+      <c r="D19" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
@@ -881,7 +1046,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
         <v>55</v>
@@ -895,7 +1060,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B26" t="s">
         <v>55</v>
@@ -909,7 +1074,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="B27" t="s">
         <v>55</v>
@@ -923,7 +1088,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
         <v>55</v>
@@ -937,7 +1102,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="B29" t="s">
         <v>55</v>
@@ -951,7 +1116,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
         <v>55</v>
@@ -965,7 +1130,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
         <v>55</v>
@@ -979,7 +1144,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s">
         <v>55</v>
@@ -993,7 +1158,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="B33" t="s">
         <v>56</v>
@@ -1007,7 +1172,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="B34" t="s">
         <v>56</v>
@@ -1021,7 +1186,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="B35" t="s">
         <v>56</v>
@@ -1035,7 +1200,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="B36" t="s">
         <v>56</v>
@@ -1049,104 +1214,311 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>23</v>
+      </c>
+      <c r="D38" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>60</v>
+        <v>23</v>
+      </c>
+      <c r="D39" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
         <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>60</v>
+      </c>
+      <c r="D42" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C43" t="s">
-        <v>68</v>
+        <v>60</v>
+      </c>
+      <c r="D43" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>67</v>
+      </c>
+      <c r="B45" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>75</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B47" t="s">
         <v>77</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C47" t="s">
         <v>76</v>
       </c>
+      <c r="D47" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>80</v>
+      </c>
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>81</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>89</v>
+      </c>
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>93</v>
+      </c>
+      <c r="B54" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" t="s">
+        <v>41</v>
+      </c>
+      <c r="D56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="3">
+        <v>100</v>
+      </c>
+      <c r="C57" t="s">
+        <v>23</v>
+      </c>
+      <c r="D57" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" t="s">
+        <v>23</v>
+      </c>
+      <c r="D58" t="s">
+        <v>82</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A48:D48"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>